--- a/data/trans_orig/Hacinamiento-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de personas que viven en el hogar</t>
+          <t>Número de personas que viven en el hogar (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,56</t>
+          <t>1,37; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,56</t>
+          <t>1,34; 1,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,48</t>
+          <t>1,3; 1,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,45</t>
+          <t>1,26; 1,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,48</t>
+          <t>1,35; 1,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,48</t>
+          <t>1,32; 1,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,53</t>
+          <t>1,35; 1,52</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,37</t>
+          <t>1,3; 1,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,29</t>
+          <t>1,22; 1,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,26</t>
+          <t>1,22; 1,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,22</t>
+          <t>1,13; 1,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,32</t>
+          <t>1,21; 1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,28</t>
+          <t>1,17; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,19</t>
+          <t>1,1; 1,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,19</t>
+          <t>1,13; 1,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,3</t>
+          <t>1,25; 1,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Estudios-trans_orig.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,54</t>
+          <t>1,34; 1,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,55</t>
+          <t>1,36; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,58</t>
+          <t>1,32; 1,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,49</t>
+          <t>1,29; 1,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,46</t>
+          <t>1,27; 1,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,46</t>
+          <t>1,33; 1,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,49</t>
+          <t>1,35; 1,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,52</t>
+          <t>1,36; 1,52</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,31</t>
+          <t>1,26; 1,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,3</t>
+          <t>1,22; 1,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,27</t>
+          <t>1,22; 1,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,27</t>
+          <t>1,22; 1,26</t>
         </is>
       </c>
     </row>
@@ -1011,22 +1011,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>1,18; 1,28</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,15; 1,26</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>1,17; 1,28</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 1,26</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 1,29</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,19</t>
+          <t>1,11; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,3</t>
+          <t>1,24; 1,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,27</t>
+          <t>1,21; 1,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,54</t>
+          <t>1,27; 1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,55</t>
+          <t>1,29; 1,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,57</t>
+          <t>1,27; 1,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,47</t>
+          <t>1,37; 1,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,43</t>
+          <t>1,35; 1,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,49</t>
+          <t>1,37; 1,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,46</t>
+          <t>1,32; 1,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,62</t>
+          <t>1,22; 1,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,47</t>
+          <t>1,33; 1,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,48</t>
+          <t>1,36; 1,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,47</t>
+          <t>1,32; 1,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,52</t>
+          <t>1,33; 1,52</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>1,23</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,44 +856,44 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,31</t>
+          <t>1,26; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1,29; 1,37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1,2; 1,26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1,21; 1,29</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,25; 1,31</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1,28; 1,35</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1,22; 1,29</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1,2; 1,26</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,26; 1,33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,3; 1,37</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 1,26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 1,29</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1,27; 1,31</t>
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,26</t>
+          <t>1,21; 1,26</t>
         </is>
       </c>
     </row>
@@ -928,62 +928,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,17</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -996,42 +996,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,23</t>
+          <t>1,16; 1,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,32</t>
+          <t>1,17; 1,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>1,11; 1,19</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,13; 1,22</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,13; 1,22</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,32</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>1,12; 1,22</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,28</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 1,26</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 1,28</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 1,2</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,24</t>
+          <t>1,18; 1,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,19</t>
+          <t>1,12; 1,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,24</t>
+          <t>1,16; 1,23</t>
         </is>
       </c>
     </row>
@@ -1068,62 +1068,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1136,44 +1136,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,29</t>
+          <t>1,25; 1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1,28; 1,34</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 1,25</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,28</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,25; 1,3</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>1,29; 1,35</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,27</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,27</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>1,21; 1,26</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,31</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 1,34</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,25</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,29</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1,26; 1,29</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,27</t>
+          <t>1,22; 1,26</t>
         </is>
       </c>
     </row>
